--- a/backtest_runs/20260410_193731/by_symbol/PAKT/PAKT.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/PAKT/PAKT.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-2348.58000000001</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>97651.41999999998</v>
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>97651.41999999998</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>97651.41999999998</v>
@@ -771,7 +771,7 @@
         <v>-55.3799999999851</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>102263.56</v>
@@ -909,7 +909,7 @@
         <v>-3912.480000000006</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>101001.52</v>
@@ -1185,7 +1185,7 @@
         <v>-1343.939999999984</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>103258.84</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>103258.84</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>103258.84</v>
@@ -1323,7 +1323,7 @@
         <v>-2118.480000000006</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>101140.36</v>
@@ -1461,7 +1461,7 @@
         <v>-1898.520000000011</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>102798.64</v>
@@ -1553,7 +1553,7 @@
         <v>-673.9200000000078</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>102346.24</v>
